--- a/Team-Data/2012-13/3-17-2012-13.xlsx
+++ b/Team-Data/2012-13/3-17-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,43 +728,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
         <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J2" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L2" t="n">
         <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="N2" t="n">
         <v>0.379</v>
       </c>
       <c r="O2" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="Q2" t="n">
         <v>0.706</v>
@@ -706,40 +773,40 @@
         <v>9.300000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T2" t="n">
         <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V2" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
         <v>18.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -760,7 +827,7 @@
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL2" t="n">
         <v>3</v>
@@ -778,7 +845,7 @@
         <v>28</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR2" t="n">
         <v>26</v>
@@ -793,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -814,7 +881,7 @@
         <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF3" t="n">
         <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -942,7 +1009,7 @@
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
@@ -978,7 +1045,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
         <v>38</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.576</v>
+        <v>0.585</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,10 +1110,10 @@
         <v>35.1</v>
       </c>
       <c r="J4" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L4" t="n">
         <v>7.8</v>
@@ -1061,19 +1128,19 @@
         <v>17.3</v>
       </c>
       <c r="P4" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0.734</v>
       </c>
       <c r="R4" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S4" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T4" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U4" t="n">
         <v>20.1</v>
@@ -1091,7 +1158,7 @@
         <v>4.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA4" t="n">
         <v>21.2</v>
@@ -1100,10 +1167,10 @@
         <v>95.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,10 +1200,10 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP4" t="n">
         <v>8</v>
@@ -1148,22 +1215,22 @@
         <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1178,7 +1245,7 @@
         <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-10.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1321,7 +1388,7 @@
         <v>4</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>20</v>
@@ -1488,7 +1555,7 @@
         <v>19</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1518,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>14</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
         <v>26</v>
@@ -1670,7 +1737,7 @@
         <v>4</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
         <v>16</v>
@@ -1685,7 +1752,7 @@
         <v>11</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>16</v>
@@ -1700,7 +1767,7 @@
         <v>25</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
         <v>6</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
         <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>0.47</v>
+        <v>0.477</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
@@ -1783,7 +1850,7 @@
         <v>20.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O8" t="n">
         <v>16.6</v>
@@ -1792,31 +1859,31 @@
         <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
       <c r="R8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
         <v>14.2</v>
       </c>
       <c r="W8" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X8" t="n">
         <v>5.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z8" t="n">
         <v>21</v>
@@ -1828,19 +1895,19 @@
         <v>101.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
       </c>
       <c r="AF8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1867,7 +1934,7 @@
         <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
         <v>2</v>
@@ -1876,10 +1943,10 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>4.9</v>
       </c>
       <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="n">
         <v>4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>5</v>
       </c>
       <c r="AF9" t="n">
         <v>6</v>
@@ -2037,7 +2104,7 @@
         <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>19</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -2201,13 +2268,13 @@
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2231,7 +2298,7 @@
         <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
         <v>28</v>
@@ -2240,7 +2307,7 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
         <v>12</v>
@@ -2255,7 +2322,7 @@
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
         <v>20</v>
@@ -2267,7 +2334,7 @@
         <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
         <v>26</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
         <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.552</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J11" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="K11" t="n">
         <v>0.454</v>
@@ -2326,16 +2393,16 @@
         <v>7.9</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.398</v>
+        <v>0.396</v>
       </c>
       <c r="O11" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P11" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>0.791</v>
@@ -2344,16 +2411,16 @@
         <v>10.9</v>
       </c>
       <c r="S11" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="T11" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
         <v>22.4</v>
       </c>
       <c r="V11" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W11" t="n">
         <v>6.8</v>
@@ -2368,28 +2435,28 @@
         <v>21.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>10</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>16</v>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2431,10 +2498,10 @@
         <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
@@ -2446,7 +2513,7 @@
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -2481,58 +2548,58 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" t="n">
         <v>36</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" t="n">
-        <v>0.537</v>
+        <v>0.545</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="J12" t="n">
         <v>82.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.463</v>
+        <v>0.465</v>
       </c>
       <c r="L12" t="n">
         <v>10.8</v>
       </c>
       <c r="M12" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="N12" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O12" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P12" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R12" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U12" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V12" t="n">
         <v>16.4</v>
@@ -2547,25 +2614,25 @@
         <v>6.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
         <v>20.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.5</v>
+        <v>106.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
         <v>14</v>
@@ -2574,13 +2641,13 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ12" t="n">
         <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2595,13 +2662,13 @@
         <v>2</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2622,7 +2689,7 @@
         <v>28</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
@@ -2631,7 +2698,7 @@
         <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
         <v>8</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
       </c>
       <c r="AF13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="n">
         <v>7</v>
@@ -2771,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO13" t="n">
         <v>15</v>
@@ -2786,7 +2853,7 @@
         <v>3</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
         <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J14" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.477</v>
@@ -2872,58 +2939,58 @@
         <v>7.5</v>
       </c>
       <c r="M14" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O14" t="n">
         <v>16.5</v>
       </c>
       <c r="P14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.705</v>
+        <v>0.708</v>
       </c>
       <c r="R14" t="n">
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
         <v>14.8</v>
       </c>
       <c r="W14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z14" t="n">
         <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2941,7 +3008,7 @@
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
         <v>5</v>
@@ -2950,10 +3017,10 @@
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
         <v>18</v>
@@ -2962,16 +3029,16 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -2992,7 +3059,7 @@
         <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
         <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>0.529</v>
+        <v>0.522</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,19 +3112,19 @@
         <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L15" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O15" t="n">
         <v>19</v>
@@ -3069,16 +3136,16 @@
         <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V15" t="n">
         <v>15.1</v>
@@ -3093,22 +3160,22 @@
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AF15" t="n">
         <v>15</v>
@@ -3123,10 +3190,10 @@
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
         <v>3</v>
@@ -3147,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
         <v>2</v>
@@ -3162,13 +3229,13 @@
         <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
@@ -3302,7 +3369,7 @@
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
@@ -3353,7 +3420,7 @@
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>18</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.785</v>
+        <v>0.781</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3409,10 +3476,10 @@
         <v>38.9</v>
       </c>
       <c r="J17" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.496</v>
+        <v>0.495</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
@@ -3421,28 +3488,28 @@
         <v>20.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
         <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R17" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="S17" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T17" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="U17" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V17" t="n">
         <v>13.5</v>
@@ -3451,7 +3518,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y17" t="n">
         <v>3.2</v>
@@ -3466,13 +3533,13 @@
         <v>103.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>1</v>
@@ -3496,16 +3563,16 @@
         <v>7</v>
       </c>
       <c r="AM17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN17" t="n">
         <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3514,22 +3581,22 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
         <v>32</v>
       </c>
       <c r="G18" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3597,22 +3664,22 @@
         <v>0.438</v>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M18" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.742</v>
+        <v>0.739</v>
       </c>
       <c r="R18" t="n">
         <v>12.6</v>
@@ -3621,7 +3688,7 @@
         <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U18" t="n">
         <v>22.9</v>
@@ -3639,19 +3706,19 @@
         <v>4.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA18" t="n">
         <v>19.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3681,7 +3748,7 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
@@ -3690,7 +3757,7 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
@@ -3702,13 +3769,13 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV18" t="n">
         <v>9</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>8</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3720,10 +3787,10 @@
         <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
         <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>0.359</v>
+        <v>0.349</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,10 +3840,10 @@
         <v>35.5</v>
       </c>
       <c r="J19" t="n">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.434</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
@@ -3785,13 +3852,13 @@
         <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.299</v>
+        <v>0.298</v>
       </c>
       <c r="O19" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P19" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0.73</v>
@@ -3800,34 +3867,34 @@
         <v>12.4</v>
       </c>
       <c r="S19" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T19" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
         <v>8.1</v>
       </c>
       <c r="X19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
         <v>18.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC19" t="n">
         <v>-3.3</v>
@@ -3836,13 +3903,13 @@
         <v>29</v>
       </c>
       <c r="AE19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF19" t="n">
         <v>22</v>
       </c>
-      <c r="AF19" t="n">
-        <v>21</v>
-      </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3851,10 +3918,10 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3875,28 +3942,28 @@
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
         <v>13</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,7 +4022,7 @@
         <v>36.4</v>
       </c>
       <c r="J20" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K20" t="n">
         <v>0.452</v>
@@ -3979,10 +4046,10 @@
         <v>0.772</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T20" t="n">
         <v>41.2</v>
@@ -3991,7 +4058,7 @@
         <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W20" t="n">
         <v>6.3</v>
@@ -4000,7 +4067,7 @@
         <v>5.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>20.4</v>
@@ -4009,22 +4076,22 @@
         <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG20" t="n">
         <v>26</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>27</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4033,13 +4100,13 @@
         <v>20</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
@@ -4054,10 +4121,10 @@
         <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4069,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4078,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -4119,46 +4186,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="n">
         <v>38</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>0.594</v>
+        <v>0.603</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
         <v>81.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
         <v>10.7</v>
       </c>
       <c r="M21" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.368</v>
+        <v>0.366</v>
       </c>
       <c r="O21" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R21" t="n">
         <v>11.1</v>
@@ -4170,31 +4237,31 @@
         <v>41.1</v>
       </c>
       <c r="U21" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V21" t="n">
         <v>12.2</v>
       </c>
       <c r="W21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X21" t="n">
         <v>3.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD21" t="n">
         <v>29</v>
@@ -4227,10 +4294,10 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP21" t="n">
         <v>17</v>
@@ -4239,10 +4306,10 @@
         <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
         <v>22</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ21" t="n">
         <v>13</v>
@@ -4269,7 +4336,7 @@
         <v>21</v>
       </c>
       <c r="BB21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC21" t="n">
         <v>9</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
         <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.746</v>
+        <v>0.742</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4331,10 +4398,10 @@
         <v>19.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.387</v>
+        <v>0.389</v>
       </c>
       <c r="O22" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="P22" t="n">
         <v>27.3</v>
@@ -4364,10 +4431,10 @@
         <v>7.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
         <v>21.1</v>
@@ -4379,7 +4446,7 @@
         <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ22" t="n">
         <v>18</v>
@@ -4451,7 +4518,7 @@
         <v>7</v>
       </c>
       <c r="BB22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -4483,46 +4550,46 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" t="n">
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>0.269</v>
+        <v>0.273</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="J23" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L23" t="n">
         <v>6.5</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="O23" t="n">
         <v>12.4</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.771</v>
+        <v>0.773</v>
       </c>
       <c r="R23" t="n">
         <v>10.5</v>
@@ -4537,10 +4604,10 @@
         <v>23.2</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
@@ -4549,19 +4616,19 @@
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>-6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4609,13 +4676,13 @@
         <v>11</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU23" t="n">
         <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4624,7 +4691,7 @@
         <v>26</v>
       </c>
       <c r="AY23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ23" t="n">
         <v>11</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
@@ -4761,10 +4828,10 @@
         <v>14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4773,7 +4840,7 @@
         <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4992,19 @@
         <v>-6.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
@@ -4964,13 +5031,13 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS25" t="n">
         <v>21</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -4982,7 +5049,7 @@
         <v>28</v>
       </c>
       <c r="AW25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -4997,7 +5064,7 @@
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5137,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
         <v>21</v>
@@ -5149,13 +5216,13 @@
         <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
         <v>16</v>
       </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
@@ -5170,7 +5237,7 @@
         <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="n">
         <v>23</v>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G27" t="n">
-        <v>0.343</v>
+        <v>0.348</v>
       </c>
       <c r="H27" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J27" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K27" t="n">
         <v>0.445</v>
@@ -5238,19 +5305,19 @@
         <v>7.2</v>
       </c>
       <c r="M27" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O27" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="P27" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R27" t="n">
         <v>11.6</v>
@@ -5259,16 +5326,16 @@
         <v>28.9</v>
       </c>
       <c r="T27" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U27" t="n">
         <v>20.6</v>
       </c>
       <c r="V27" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X27" t="n">
         <v>4.2</v>
@@ -5280,16 +5347,16 @@
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB27" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5301,40 +5368,40 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>13</v>
       </c>
       <c r="AJ27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK27" t="n">
         <v>17</v>
       </c>
       <c r="AL27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM27" t="n">
         <v>15</v>
       </c>
       <c r="AN27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT27" t="n">
         <v>26</v>
@@ -5343,7 +5410,7 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW27" t="n">
         <v>7</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5525,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>0.388</v>
+        <v>0.394</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
@@ -5593,49 +5660,49 @@
         <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M29" t="n">
         <v>20.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.346</v>
+        <v>0.35</v>
       </c>
       <c r="O29" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P29" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.785</v>
+        <v>0.784</v>
       </c>
       <c r="R29" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="S29" t="n">
         <v>29.3</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V29" t="n">
         <v>13.5</v>
       </c>
       <c r="W29" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
         <v>5</v>
@@ -5644,22 +5711,22 @@
         <v>22.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
         <v>20</v>
@@ -5668,7 +5735,7 @@
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ29" t="n">
         <v>11</v>
@@ -5677,16 +5744,16 @@
         <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5695,7 +5762,7 @@
         <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5707,16 +5774,16 @@
         <v>20</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW29" t="n">
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5847,7 +5914,7 @@
         <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI30" t="n">
         <v>18</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
@@ -5877,10 +5944,10 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
@@ -5898,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>22</v>
@@ -6026,7 +6093,7 @@
         <v>23</v>
       </c>
       <c r="AG31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH31" t="n">
         <v>5</v>
@@ -6041,7 +6108,7 @@
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM31" t="n">
         <v>20</v>
@@ -6059,7 +6126,7 @@
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -6068,7 +6135,7 @@
         <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-17-2012-13</t>
+          <t>2013-03-17</t>
         </is>
       </c>
     </row>
